--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\csv2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\paiza-training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01A0BF9-76B0-4067-96A8-2A4114D89360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F909BA7D-EA5D-4440-A702-1BBAB06798C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1680" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>日付</t>
   </si>
@@ -112,6 +112,24 @@
   </si>
   <si>
     <t>4分02秒</t>
+    <rPh sb="1" eb="2">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D350</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution_1.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4分10秒</t>
     <rPh sb="1" eb="2">
       <t>フン</t>
     </rPh>
@@ -575,11 +593,21 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="B4" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1">
+        <v>100</v>
+      </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7">
@@ -1092,5 +1120,6 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F909BA7D-EA5D-4440-A702-1BBAB06798C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F1EFA3-9832-4858-83EB-7621E0DA0580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>日付</t>
   </si>
@@ -130,6 +130,34 @@
   </si>
   <si>
     <t>4分10秒</t>
+    <rPh sb="1" eb="2">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D156</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3分15秒</t>
+    <rPh sb="1" eb="2">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>D214</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1分59秒</t>
     <rPh sb="1" eb="2">
       <t>フン</t>
     </rPh>
@@ -614,22 +642,42 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="B5" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1">
+        <v>100</v>
+      </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="B6" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1">
+        <v>100</v>
+      </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F1EFA3-9832-4858-83EB-7621E0DA0580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E3BBD-78DB-43E1-A262-7876FEB26C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>日付</t>
   </si>
@@ -158,6 +158,20 @@
   </si>
   <si>
     <t>1分59秒</t>
+    <rPh sb="1" eb="2">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C166</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5分30秒</t>
     <rPh sb="1" eb="2">
       <t>フン</t>
     </rPh>
@@ -684,6 +698,21 @@
       <c r="A7">
         <v>4</v>
       </c>
+      <c r="B7" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E3BBD-78DB-43E1-A262-7876FEB26C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8F2366-0C9E-4052-B35F-05B6AB117DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>日付</t>
   </si>
@@ -173,6 +173,20 @@
   <si>
     <t>5分30秒</t>
     <rPh sb="1" eb="2">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C099</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>22分5秒</t>
+    <rPh sb="2" eb="3">
       <t>フン</t>
     </rPh>
     <rPh sb="4" eb="5">
@@ -718,6 +732,21 @@
       <c r="A8">
         <v>5</v>
       </c>
+      <c r="B8" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8F2366-0C9E-4052-B35F-05B6AB117DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29DC59D-1964-4BEC-A575-04DA7D1ABA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>日付</t>
   </si>
@@ -192,6 +192,14 @@
     <rPh sb="4" eb="5">
       <t>ビョウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>35分37秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C102</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -752,6 +760,21 @@
       <c r="A9">
         <v>6</v>
       </c>
+      <c r="B9" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29DC59D-1964-4BEC-A575-04DA7D1ABA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A792E656-BCAD-4599-B012-E3D3DCC3BD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>日付</t>
   </si>
@@ -200,6 +200,14 @@
   </si>
   <si>
     <t>C102</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>69分5秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B136</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -780,6 +788,21 @@
       <c r="A10">
         <v>7</v>
       </c>
+      <c r="B10" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A792E656-BCAD-4599-B012-E3D3DCC3BD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702B5D52-50A0-4120-9F75-8411D105A340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>日付</t>
   </si>
@@ -208,6 +208,18 @@
   </si>
   <si>
     <t>B136</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>54分55秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B145</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -808,6 +820,21 @@
       <c r="A11">
         <v>8</v>
       </c>
+      <c r="B11" s="7">
+        <v>45874</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a-saito\Documents\教育\入社教育\2. C#基礎\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702B5D52-50A0-4120-9F75-8411D105A340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818FE3C6-C97A-48F5-BA26-433E016568EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1680" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>日付</t>
   </si>
@@ -220,6 +220,66 @@
   </si>
   <si>
     <t>B145</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半日で初のBランククリアおめでとうございます！
+Paizaのブログ記事を検索するとわかりますが、ここに来るまでで１か月かかることもざらではありません。実は1~2週間はスキルチェックしながら文法や作法を学習してもらおうと思っていたので、この調子で複数クリアおよび、さらに高ランクの課題にも挑戦しください。</t>
+    <rPh sb="0" eb="2">
+      <t>ハンニチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ブンポウ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>サホウ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>チョウシ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="134" eb="135">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>チョウセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>paizaの回答結果ページに模範解答が載っていると思います。C#ではなくjavaとかだったと思いますが、そのコードをchatGPTなどにコピペして「C#に変換してください」と伝えると、簡単ですがC#版回答が得られますので参考にされてください（paizaの規約にありますが、AIの生成したコードをそのままpaizaに流さないように注意してください）。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -289,16 +349,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -314,6 +371,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,42 +664,42 @@
   <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="8"/>
-    <col min="4" max="4" width="12.625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="8" customWidth="1"/>
-    <col min="7" max="7" width="27.75" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="7"/>
+    <col min="4" max="4" width="12.625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="7" customWidth="1"/>
+    <col min="7" max="7" width="49.25" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickTop="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>45871</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -645,7 +711,7 @@
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>100</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -653,10 +719,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>45871</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -668,16 +734,16 @@
       <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>80</v>
       </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>45874</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -695,10 +761,10 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5">
+      <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>45874</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -716,10 +782,10 @@
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6">
+      <c r="A6" s="10">
         <v>3</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>45874</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -737,564 +803,1125 @@
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7">
+      <c r="A7" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>45874</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="1">
         <v>100</v>
       </c>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8">
+      <c r="A8" s="10">
         <v>5</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>45874</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="1">
         <v>100</v>
       </c>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9">
+      <c r="A9" s="10">
         <v>6</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>45874</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" ht="112.5">
+      <c r="A10" s="10">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>45874</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
+      <c r="G10" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="131.25">
+      <c r="A11" s="10">
         <v>8</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>45874</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="1">
         <v>0</v>
       </c>
+      <c r="G11" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12">
+      <c r="A12" s="10">
         <v>9</v>
       </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13">
+      <c r="A13" s="10">
         <v>10</v>
       </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14">
+      <c r="A14" s="10">
         <v>11</v>
       </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15">
+      <c r="A15" s="10">
         <v>12</v>
       </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16">
+      <c r="A16" s="10">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="10">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="10">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="10">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="10">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="10">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="10">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="10">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="10">
         <v>21</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="10">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="10">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="10">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="10">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="10">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="10">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="10">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="10">
         <v>29</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="10">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="10">
         <v>31</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="10">
         <v>32</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="10">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="10">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="10">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="10">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
         <v>37</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
         <v>38</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
         <v>39</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
         <v>40</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
         <v>41</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
         <v>42</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="10">
         <v>43</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10">
         <v>44</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="10">
         <v>46</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="10">
         <v>47</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="10">
         <v>48</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="10">
         <v>49</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="10">
         <v>50</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54">
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="10">
         <v>51</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="10">
         <v>52</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="10">
         <v>53</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="10">
         <v>54</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="10">
         <v>55</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="10">
         <v>56</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="10">
         <v>57</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="10">
         <v>58</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="10">
         <v>59</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63">
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="10">
         <v>60</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="10">
         <v>61</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="10">
         <v>62</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66">
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="10">
         <v>63</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="10">
         <v>64</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="10">
         <v>65</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="10">
         <v>66</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="10">
         <v>67</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="10">
         <v>68</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="10">
         <v>69</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="10">
         <v>70</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="10">
         <v>71</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="10">
         <v>72</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="10">
         <v>73</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="10">
         <v>74</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="10">
         <v>75</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79">
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="10">
         <v>76</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80">
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="10">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="10">
         <v>78</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="10">
         <v>79</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83">
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="10">
         <v>80</v>
       </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84">
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="10">
         <v>81</v>
       </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="10">
         <v>82</v>
       </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86">
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="10">
         <v>83</v>
       </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87">
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="10">
         <v>84</v>
       </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88">
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="10">
         <v>85</v>
       </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89">
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="10">
         <v>86</v>
       </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90">
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="10">
         <v>87</v>
       </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="10">
         <v>88</v>
       </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92">
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="10">
         <v>89</v>
       </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93">
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="10">
         <v>90</v>
       </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94">
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="10">
         <v>91</v>
       </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95">
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="10">
         <v>92</v>
       </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96">
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="10">
         <v>93</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97">
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="10">
         <v>94</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98">
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="10">
         <v>95</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99">
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="10">
         <v>96</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100">
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="10">
         <v>97</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="10">
         <v>98</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102">
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="10">
         <v>99</v>
       </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103">
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="10">
         <v>100</v>
       </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a-saito\Documents\教育\入社教育\2. C#基礎\paiza-training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818FE3C6-C97A-48F5-BA26-433E016568EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027F230E-3950-415B-99A6-73DA74FFDFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1680" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>日付</t>
   </si>
@@ -280,6 +280,14 @@
   </si>
   <si>
     <t>paizaの回答結果ページに模範解答が載っていると思います。C#ではなくjavaとかだったと思いますが、そのコードをchatGPTなどにコピペして「C#に変換してください」と伝えると、簡単ですがC#版回答が得られますので参考にされてください（paizaの規約にありますが、AIの生成したコードをそのままpaizaに流さないように注意してください）。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution_2.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>／</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -915,11 +923,21 @@
       <c r="A12" s="10">
         <v>9</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="B12" s="6">
+        <v>45875</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1">
+        <v>100</v>
+      </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027F230E-3950-415B-99A6-73DA74FFDFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DB4CAE-B501-451B-A457-A1BDFB4B4EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>日付</t>
   </si>
@@ -288,6 +288,10 @@
   </si>
   <si>
     <t>／</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution_3.cs</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -944,11 +948,21 @@
       <c r="A13" s="10">
         <v>10</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="B13" s="6">
+        <v>45875</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="1">
+        <v>100</v>
+      </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DB4CAE-B501-451B-A457-A1BDFB4B4EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F163990-0BD9-4387-B2A0-B378EFCA20D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>日付</t>
   </si>
@@ -292,6 +292,20 @@
   </si>
   <si>
     <t>solution_3.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B067</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>223分8秒</t>
+    <rPh sb="3" eb="4">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ビョウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -969,11 +983,21 @@
       <c r="A14" s="10">
         <v>11</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="B14" s="6">
+        <v>45875</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F163990-0BD9-4387-B2A0-B378EFCA20D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3EA5E7-684A-4A8D-9B5A-3117361A0F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>日付</t>
   </si>
@@ -1004,11 +1004,21 @@
       <c r="A15" s="10">
         <v>12</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="B15" s="6">
+        <v>45875</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="1">
+        <v>90</v>
+      </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3EA5E7-684A-4A8D-9B5A-3117361A0F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCCBC29-C2FF-4A19-9D95-B89B22C03071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>日付</t>
   </si>
@@ -306,6 +306,14 @@
     <rPh sb="5" eb="6">
       <t>ビョウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>51分59秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B138</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1025,11 +1033,21 @@
       <c r="A16" s="10">
         <v>13</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" s="6">
+        <v>45875</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="1">
+        <v>100</v>
+      </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCCBC29-C2FF-4A19-9D95-B89B22C03071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB0DE56-9D4E-4713-8FD4-34BD801E517D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>日付</t>
   </si>
@@ -314,6 +314,14 @@
   </si>
   <si>
     <t>B138</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B045</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 79分14秒</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1054,11 +1062,21 @@
       <c r="A17" s="10">
         <v>14</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="B17" s="6">
+        <v>45875</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB0DE56-9D4E-4713-8FD4-34BD801E517D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B4ADD3-496D-47AF-A520-4D27AF2A645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t>日付</t>
   </si>
@@ -1083,11 +1083,21 @@
       <c r="A18" s="10">
         <v>15</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="B18" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="1">
+        <v>100</v>
+      </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B4ADD3-496D-47AF-A520-4D27AF2A645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA37E3B-46FE-412A-90F8-6960808A23FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -322,6 +322,14 @@
   </si>
   <si>
     <t xml:space="preserve"> 79分14秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution_4.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>solution_5.cs</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1104,22 +1112,42 @@
       <c r="A19" s="10">
         <v>16</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="B19" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="1">
+        <v>100</v>
+      </c>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="B20" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="1">
+        <v>100</v>
+      </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA37E3B-46FE-412A-90F8-6960808A23FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA5FB31-284D-4940-8C4F-3564A3F667A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>日付</t>
   </si>
@@ -330,6 +330,14 @@
   </si>
   <si>
     <t>solution_5.cs</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>123分57秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>A078</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1154,11 +1162,21 @@
       <c r="A21" s="10">
         <v>18</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="B21" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="1">
+        <v>80</v>
+      </c>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA5FB31-284D-4940-8C4F-3564A3F667A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EFCBAE-2125-4FA9-B7C2-1B9465883FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
   <si>
     <t>日付</t>
   </si>
@@ -1153,9 +1153,6 @@
       <c r="E20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="1">
-        <v>100</v>
-      </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
@@ -1183,11 +1180,21 @@
       <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="B22" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="1">
+        <v>100</v>
+      </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EFCBAE-2125-4FA9-B7C2-1B9465883FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B71E9E-FB7B-4ECE-911A-27CA0DF166EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>日付</t>
   </si>
@@ -338,6 +338,14 @@
   </si>
   <si>
     <t>A078</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>93分29秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B155</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1201,11 +1209,21 @@
       <c r="A23" s="10">
         <v>20</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B23" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B71E9E-FB7B-4ECE-911A-27CA0DF166EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB0DE56-9D4E-4713-8FD4-34BD801E517D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>日付</t>
   </si>
@@ -322,30 +322,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 79分14秒</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>solution_4.cs</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>solution_5.cs</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>123分57秒</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>A078</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>93分29秒</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>B155</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1107,123 +1083,66 @@
       <c r="A18" s="10">
         <v>15</v>
       </c>
-      <c r="B18" s="6">
-        <v>45876</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="1">
-        <v>100</v>
-      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="10">
         <v>16</v>
       </c>
-      <c r="B19" s="6">
-        <v>45876</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="1">
-        <v>100</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="6">
-        <v>45876</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="10">
         <v>18</v>
       </c>
-      <c r="B21" s="6">
-        <v>45876</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="1">
-        <v>80</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="6">
-        <v>45876</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="1">
-        <v>100</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="10">
         <v>20</v>
       </c>
-      <c r="B23" s="6">
-        <v>45876</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C45B8EB-4181-4034-B4F9-E0FD8FFE8F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t>No.</t>
   </si>
@@ -177,18 +183,25 @@
   </si>
   <si>
     <t>順調に進んでいますね。覚えることが雪だるま式に増えていきますが一歩ずついきましょう～</t>
+  </si>
+  <si>
+    <t>B155</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>solution_2.cs</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -210,6 +223,13 @@
       <color rgb="FF000000"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -248,65 +268,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -317,10 +337,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -358,71 +378,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -450,7 +470,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -473,11 +493,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -486,13 +506,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -502,7 +522,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -511,7 +531,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -520,7 +540,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -528,10 +548,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -596,23 +616,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G103"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="15" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="15" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="10.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="10.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="15" width="49.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.25" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,7 +655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="2" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -658,7 +678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -679,7 +699,7 @@
       </c>
       <c r="G3" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -700,7 +720,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -721,7 +741,7 @@
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="6" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -742,7 +762,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="7" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -763,7 +783,7 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="8" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -784,7 +804,7 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="9" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -805,7 +825,7 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="10" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -828,7 +848,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="11" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -851,7 +871,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="12" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -872,7 +892,7 @@
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="13" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -893,7 +913,7 @@
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="14" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -914,7 +934,7 @@
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="15" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -935,7 +955,7 @@
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="16" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -958,7 +978,7 @@
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="17" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -981,7 +1001,7 @@
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="18" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -1004,7 +1024,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="19" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -1027,7 +1047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="20" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -1046,7 +1066,7 @@
       <c r="F20" s="12"/>
       <c r="G20" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="21" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -1069,7 +1089,7 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="22" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -1085,12 +1105,9 @@
       <c r="E22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="10">
-        <v>100</v>
-      </c>
       <c r="G22" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25" customFormat="1" s="4">
+    <row r="23" spans="1:7" s="4" customFormat="1" ht="30">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -1113,18 +1130,28 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="24" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A24" s="5">
         <v>21</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
+      <c r="B24" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="10">
+        <v>100</v>
+      </c>
       <c r="G24" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="25" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -1135,7 +1162,7 @@
       <c r="F25" s="10"/>
       <c r="G25" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="26" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -1146,7 +1173,7 @@
       <c r="F26" s="10"/>
       <c r="G26" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="27" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -1157,7 +1184,7 @@
       <c r="F27" s="10"/>
       <c r="G27" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="28" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -1168,7 +1195,7 @@
       <c r="F28" s="10"/>
       <c r="G28" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="29" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -1179,7 +1206,7 @@
       <c r="F29" s="10"/>
       <c r="G29" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="30" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A30" s="5">
         <v>27</v>
       </c>
@@ -1190,7 +1217,7 @@
       <c r="F30" s="10"/>
       <c r="G30" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="31" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A31" s="5">
         <v>28</v>
       </c>
@@ -1201,7 +1228,7 @@
       <c r="F31" s="10"/>
       <c r="G31" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="32" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A32" s="5">
         <v>29</v>
       </c>
@@ -1212,7 +1239,7 @@
       <c r="F32" s="10"/>
       <c r="G32" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="33" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A33" s="5">
         <v>30</v>
       </c>
@@ -1223,7 +1250,7 @@
       <c r="F33" s="10"/>
       <c r="G33" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="34" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A34" s="5">
         <v>31</v>
       </c>
@@ -1234,7 +1261,7 @@
       <c r="F34" s="10"/>
       <c r="G34" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="35" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A35" s="5">
         <v>32</v>
       </c>
@@ -1245,7 +1272,7 @@
       <c r="F35" s="10"/>
       <c r="G35" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="36" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -1256,7 +1283,7 @@
       <c r="F36" s="10"/>
       <c r="G36" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="37" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A37" s="5">
         <v>34</v>
       </c>
@@ -1267,7 +1294,7 @@
       <c r="F37" s="10"/>
       <c r="G37" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="38" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A38" s="5">
         <v>35</v>
       </c>
@@ -1278,7 +1305,7 @@
       <c r="F38" s="10"/>
       <c r="G38" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="39" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A39" s="5">
         <v>36</v>
       </c>
@@ -1289,7 +1316,7 @@
       <c r="F39" s="10"/>
       <c r="G39" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="40" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A40" s="5">
         <v>37</v>
       </c>
@@ -1300,7 +1327,7 @@
       <c r="F40" s="10"/>
       <c r="G40" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="41" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A41" s="5">
         <v>38</v>
       </c>
@@ -1311,7 +1338,7 @@
       <c r="F41" s="10"/>
       <c r="G41" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="42" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A42" s="5">
         <v>39</v>
       </c>
@@ -1322,7 +1349,7 @@
       <c r="F42" s="10"/>
       <c r="G42" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="43" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A43" s="5">
         <v>40</v>
       </c>
@@ -1333,7 +1360,7 @@
       <c r="F43" s="10"/>
       <c r="G43" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="44" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A44" s="5">
         <v>41</v>
       </c>
@@ -1344,7 +1371,7 @@
       <c r="F44" s="10"/>
       <c r="G44" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="45" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A45" s="5">
         <v>42</v>
       </c>
@@ -1355,7 +1382,7 @@
       <c r="F45" s="10"/>
       <c r="G45" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="46" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A46" s="5">
         <v>43</v>
       </c>
@@ -1366,7 +1393,7 @@
       <c r="F46" s="10"/>
       <c r="G46" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="47" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A47" s="5">
         <v>44</v>
       </c>
@@ -1377,7 +1404,7 @@
       <c r="F47" s="10"/>
       <c r="G47" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="48" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A48" s="5">
         <v>45</v>
       </c>
@@ -1388,7 +1415,7 @@
       <c r="F48" s="10"/>
       <c r="G48" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="49" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A49" s="5">
         <v>46</v>
       </c>
@@ -1399,7 +1426,7 @@
       <c r="F49" s="10"/>
       <c r="G49" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="50" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A50" s="5">
         <v>47</v>
       </c>
@@ -1410,7 +1437,7 @@
       <c r="F50" s="10"/>
       <c r="G50" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="51" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A51" s="5">
         <v>48</v>
       </c>
@@ -1421,7 +1448,7 @@
       <c r="F51" s="10"/>
       <c r="G51" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="52" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A52" s="5">
         <v>49</v>
       </c>
@@ -1432,7 +1459,7 @@
       <c r="F52" s="10"/>
       <c r="G52" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="53" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A53" s="5">
         <v>50</v>
       </c>
@@ -1443,7 +1470,7 @@
       <c r="F53" s="10"/>
       <c r="G53" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="54" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A54" s="5">
         <v>51</v>
       </c>
@@ -1454,7 +1481,7 @@
       <c r="F54" s="10"/>
       <c r="G54" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="55" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A55" s="5">
         <v>52</v>
       </c>
@@ -1465,7 +1492,7 @@
       <c r="F55" s="10"/>
       <c r="G55" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="56" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A56" s="5">
         <v>53</v>
       </c>
@@ -1476,7 +1503,7 @@
       <c r="F56" s="10"/>
       <c r="G56" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="57" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A57" s="5">
         <v>54</v>
       </c>
@@ -1487,7 +1514,7 @@
       <c r="F57" s="10"/>
       <c r="G57" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="58" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A58" s="5">
         <v>55</v>
       </c>
@@ -1498,7 +1525,7 @@
       <c r="F58" s="10"/>
       <c r="G58" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="59" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A59" s="5">
         <v>56</v>
       </c>
@@ -1509,7 +1536,7 @@
       <c r="F59" s="10"/>
       <c r="G59" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="60" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A60" s="5">
         <v>57</v>
       </c>
@@ -1520,7 +1547,7 @@
       <c r="F60" s="10"/>
       <c r="G60" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="61" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A61" s="5">
         <v>58</v>
       </c>
@@ -1531,7 +1558,7 @@
       <c r="F61" s="10"/>
       <c r="G61" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="62" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A62" s="5">
         <v>59</v>
       </c>
@@ -1542,7 +1569,7 @@
       <c r="F62" s="10"/>
       <c r="G62" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="63" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A63" s="5">
         <v>60</v>
       </c>
@@ -1553,7 +1580,7 @@
       <c r="F63" s="10"/>
       <c r="G63" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="64" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A64" s="5">
         <v>61</v>
       </c>
@@ -1564,7 +1591,7 @@
       <c r="F64" s="10"/>
       <c r="G64" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="65" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A65" s="5">
         <v>62</v>
       </c>
@@ -1575,7 +1602,7 @@
       <c r="F65" s="10"/>
       <c r="G65" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="66" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A66" s="5">
         <v>63</v>
       </c>
@@ -1586,7 +1613,7 @@
       <c r="F66" s="10"/>
       <c r="G66" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="67" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A67" s="5">
         <v>64</v>
       </c>
@@ -1597,7 +1624,7 @@
       <c r="F67" s="10"/>
       <c r="G67" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="68" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A68" s="5">
         <v>65</v>
       </c>
@@ -1608,7 +1635,7 @@
       <c r="F68" s="10"/>
       <c r="G68" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="69" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A69" s="5">
         <v>66</v>
       </c>
@@ -1619,7 +1646,7 @@
       <c r="F69" s="10"/>
       <c r="G69" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="70" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A70" s="5">
         <v>67</v>
       </c>
@@ -1630,7 +1657,7 @@
       <c r="F70" s="10"/>
       <c r="G70" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="71" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A71" s="5">
         <v>68</v>
       </c>
@@ -1641,7 +1668,7 @@
       <c r="F71" s="10"/>
       <c r="G71" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="72" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A72" s="5">
         <v>69</v>
       </c>
@@ -1652,7 +1679,7 @@
       <c r="F72" s="10"/>
       <c r="G72" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="73" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A73" s="5">
         <v>70</v>
       </c>
@@ -1663,7 +1690,7 @@
       <c r="F73" s="10"/>
       <c r="G73" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="74" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A74" s="5">
         <v>71</v>
       </c>
@@ -1674,7 +1701,7 @@
       <c r="F74" s="10"/>
       <c r="G74" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="75" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A75" s="5">
         <v>72</v>
       </c>
@@ -1685,7 +1712,7 @@
       <c r="F75" s="10"/>
       <c r="G75" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="76" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A76" s="5">
         <v>73</v>
       </c>
@@ -1696,7 +1723,7 @@
       <c r="F76" s="10"/>
       <c r="G76" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="77" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A77" s="5">
         <v>74</v>
       </c>
@@ -1707,7 +1734,7 @@
       <c r="F77" s="10"/>
       <c r="G77" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="78" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A78" s="5">
         <v>75</v>
       </c>
@@ -1718,7 +1745,7 @@
       <c r="F78" s="10"/>
       <c r="G78" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="79" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A79" s="5">
         <v>76</v>
       </c>
@@ -1729,7 +1756,7 @@
       <c r="F79" s="10"/>
       <c r="G79" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="80" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A80" s="5">
         <v>77</v>
       </c>
@@ -1740,7 +1767,7 @@
       <c r="F80" s="10"/>
       <c r="G80" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="81" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A81" s="5">
         <v>78</v>
       </c>
@@ -1751,7 +1778,7 @@
       <c r="F81" s="10"/>
       <c r="G81" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="82" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A82" s="5">
         <v>79</v>
       </c>
@@ -1762,7 +1789,7 @@
       <c r="F82" s="10"/>
       <c r="G82" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="83" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A83" s="5">
         <v>80</v>
       </c>
@@ -1773,7 +1800,7 @@
       <c r="F83" s="10"/>
       <c r="G83" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="84" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A84" s="5">
         <v>81</v>
       </c>
@@ -1784,7 +1811,7 @@
       <c r="F84" s="10"/>
       <c r="G84" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="85" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A85" s="5">
         <v>82</v>
       </c>
@@ -1795,7 +1822,7 @@
       <c r="F85" s="10"/>
       <c r="G85" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="86" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A86" s="5">
         <v>83</v>
       </c>
@@ -1806,7 +1833,7 @@
       <c r="F86" s="10"/>
       <c r="G86" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="87" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A87" s="5">
         <v>84</v>
       </c>
@@ -1817,7 +1844,7 @@
       <c r="F87" s="10"/>
       <c r="G87" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="88" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A88" s="5">
         <v>85</v>
       </c>
@@ -1828,7 +1855,7 @@
       <c r="F88" s="10"/>
       <c r="G88" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="89" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A89" s="5">
         <v>86</v>
       </c>
@@ -1839,7 +1866,7 @@
       <c r="F89" s="10"/>
       <c r="G89" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="90" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A90" s="5">
         <v>87</v>
       </c>
@@ -1850,7 +1877,7 @@
       <c r="F90" s="10"/>
       <c r="G90" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="91" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A91" s="5">
         <v>88</v>
       </c>
@@ -1861,7 +1888,7 @@
       <c r="F91" s="10"/>
       <c r="G91" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="92" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A92" s="5">
         <v>89</v>
       </c>
@@ -1872,7 +1899,7 @@
       <c r="F92" s="10"/>
       <c r="G92" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="93" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A93" s="5">
         <v>90</v>
       </c>
@@ -1883,7 +1910,7 @@
       <c r="F93" s="10"/>
       <c r="G93" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="94" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A94" s="5">
         <v>91</v>
       </c>
@@ -1894,7 +1921,7 @@
       <c r="F94" s="10"/>
       <c r="G94" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="95" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A95" s="5">
         <v>92</v>
       </c>
@@ -1905,7 +1932,7 @@
       <c r="F95" s="10"/>
       <c r="G95" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="96" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A96" s="5">
         <v>93</v>
       </c>
@@ -1916,7 +1943,7 @@
       <c r="F96" s="10"/>
       <c r="G96" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="97" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A97" s="5">
         <v>94</v>
       </c>
@@ -1927,7 +1954,7 @@
       <c r="F97" s="10"/>
       <c r="G97" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="98" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A98" s="5">
         <v>95</v>
       </c>
@@ -1938,7 +1965,7 @@
       <c r="F98" s="10"/>
       <c r="G98" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="99" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A99" s="5">
         <v>96</v>
       </c>
@@ -1949,7 +1976,7 @@
       <c r="F99" s="10"/>
       <c r="G99" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="100" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A100" s="5">
         <v>97</v>
       </c>
@@ -1960,7 +1987,7 @@
       <c r="F100" s="10"/>
       <c r="G100" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="101" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A101" s="5">
         <v>98</v>
       </c>
@@ -1971,7 +1998,7 @@
       <c r="F101" s="10"/>
       <c r="G101" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="102" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A102" s="5">
         <v>99</v>
       </c>
@@ -1982,7 +2009,7 @@
       <c r="F102" s="10"/>
       <c r="G102" s="7"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75" customFormat="1" s="4">
+    <row r="103" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A103" s="5">
         <v>100</v>
       </c>
@@ -1994,6 +2021,8 @@
       <c r="G103" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C45B8EB-4181-4034-B4F9-E0FD8FFE8F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC187DD-69DE-4392-987C-A5059A5529F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
   <si>
     <t>No.</t>
   </si>
@@ -186,18 +186,45 @@
   </si>
   <si>
     <t>B155</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>solution_2.cs</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>B023</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <t>280</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>分</t>
+    </r>
+    <rPh sb="3" eb="4">
+      <t>フン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +250,13 @@
       <color rgb="FF000000"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
@@ -1155,11 +1189,21 @@
       <c r="A25" s="5">
         <v>22</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="10"/>
+      <c r="B25" s="6">
+        <v>45876</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
@@ -2021,7 +2065,7 @@
       <c r="G103" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC187DD-69DE-4392-987C-A5059A5529F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50423AB6-2992-40AD-B783-36C88D1C0870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
   <si>
     <t>No.</t>
   </si>
@@ -1210,11 +1210,21 @@
       <c r="A26" s="5">
         <v>23</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="10"/>
+      <c r="B26" s="6">
+        <v>45887</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50423AB6-2992-40AD-B783-36C88D1C0870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D50266-297A-4E8E-9893-39AB97AAF461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -217,6 +217,10 @@
     <rPh sb="3" eb="4">
       <t>フン</t>
     </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>solution_3.cs</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1231,22 +1235,42 @@
       <c r="A27" s="5">
         <v>24</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="10"/>
+      <c r="B27" s="6">
+        <v>45887</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A28" s="5">
         <v>25</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="10"/>
+      <c r="B28" s="6">
+        <v>45887</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D50266-297A-4E8E-9893-39AB97AAF461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBC6062-FB9B-4443-8F1E-26C9D253473A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
   <si>
     <t>No.</t>
   </si>
@@ -1236,7 +1236,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="6">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>56</v>
@@ -1257,7 +1257,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="6">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>56</v>
@@ -1277,11 +1277,21 @@
       <c r="A29" s="5">
         <v>26</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="10"/>
+      <c r="B29" s="6">
+        <v>45889</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBC6062-FB9B-4443-8F1E-26C9D253473A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E890581-7C1D-4BFE-82E0-BF37EA079E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="61">
   <si>
     <t>No.</t>
   </si>
@@ -221,6 +221,10 @@
   </si>
   <si>
     <t>solution_3.cs</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>solution_4.cs</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1298,9 +1302,15 @@
       <c r="A30" s="5">
         <v>27</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="B30" s="6">
+        <v>45890</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E30" s="7"/>
       <c r="F30" s="10"/>
       <c r="G30" s="7"/>

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E890581-7C1D-4BFE-82E0-BF37EA079E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB35C91-5799-4983-8032-A1F5427E7D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
   <si>
     <t>No.</t>
   </si>
@@ -225,6 +225,33 @@
   </si>
   <si>
     <t>solution_4.cs</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>A023</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>solution_1.cs</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <t>57</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>分</t>
+    </r>
+    <rPh sb="2" eb="3">
+      <t>フン</t>
+    </rPh>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1311,19 +1338,33 @@
       <c r="D30" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="10"/>
+      <c r="E30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="10">
+        <v>100</v>
+      </c>
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A31" s="5">
         <v>28</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="10"/>
+      <c r="B31" s="6">
+        <v>45890</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="10">
+        <v>20</v>
+      </c>
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB35C91-5799-4983-8032-A1F5427E7D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF1B703-2FB6-4739-A9E5-158D45969C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>No.</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>54分55秒</t>
-  </si>
-  <si>
-    <t>paizaの回答結果ページに模範解答が載っていると思います。C#ではなくjavaとかだったと思いますが、そのコードをchatGPTなどにコピペして「C#に変換してください」と伝えると、簡単ですがC#版回答が得られますので参考にされてください（paizaの規約にありますが、AIの生成したコードをそのままpaizaに流さないように注意してください）。</t>
   </si>
   <si>
     <t>solution_2.cs</t>
@@ -254,12 +251,180 @@
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
+  <si>
+    <r>
+      <t>paiza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の回答結果ページに模範解答が載っていると思います。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ではなく</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>とかだったと思いますが、そのコードを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>chatGPT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>などにコピペして「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>に変換してください」と伝えると、簡単ですが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>版回答が得られますので参考にされてください（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>paiza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の規約にありますが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の生成したコードをそのまま</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>paiza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>に流さないように注意してください）。</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +464,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -937,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
@@ -951,10 +1123,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="F12" s="10">
         <v>100</v>
@@ -972,10 +1144,10 @@
         <v>32</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="10">
         <v>100</v>
@@ -990,13 +1162,13 @@
         <v>45875</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" s="10">
         <v>0</v>
@@ -1011,13 +1183,13 @@
         <v>45875</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="F15" s="10">
         <v>90</v>
@@ -1032,19 +1204,19 @@
         <v>45875</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="10">
         <v>100</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
@@ -1055,19 +1227,19 @@
         <v>45875</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="10">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
@@ -1078,19 +1250,19 @@
         <v>45876</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="F18" s="10">
         <v>100</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
@@ -1104,16 +1276,16 @@
         <v>32</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" s="10">
         <v>100</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
@@ -1127,10 +1299,10 @@
         <v>32</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="7"/>
@@ -1143,19 +1315,19 @@
         <v>45876</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F21" s="10">
         <v>80</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
@@ -1166,13 +1338,13 @@
         <v>45876</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="G22" s="7"/>
     </row>
@@ -1184,19 +1356,19 @@
         <v>45876</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
@@ -1207,13 +1379,13 @@
         <v>45876</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="E24" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24" s="10">
         <v>100</v>
@@ -1228,16 +1400,16 @@
         <v>45876</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="7"/>
     </row>
@@ -1249,16 +1421,16 @@
         <v>45887</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="G26" s="7"/>
     </row>
@@ -1270,16 +1442,16 @@
         <v>45888</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="G27" s="7"/>
     </row>
@@ -1291,16 +1463,16 @@
         <v>45888</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="G28" s="7"/>
     </row>
@@ -1312,16 +1484,16 @@
         <v>45889</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="G29" s="7"/>
     </row>
@@ -1333,13 +1505,13 @@
         <v>45890</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" s="10">
         <v>100</v>
@@ -1354,13 +1526,13 @@
         <v>45890</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="F31" s="10">
         <v>20</v>
@@ -1371,10 +1543,18 @@
       <c r="A32" s="5">
         <v>29</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="B32" s="6">
+        <v>45890</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="F32" s="10"/>
       <c r="G32" s="7"/>
     </row>

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF1B703-2FB6-4739-A9E5-158D45969C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A33474F-8720-40F3-BFBA-51223F3A2B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -419,12 +419,51 @@
     </r>
     <phoneticPr fontId="5"/>
   </si>
+  <si>
+    <r>
+      <t>87</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>秒</t>
+    </r>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>A057</t>
+    <phoneticPr fontId="5"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,6 +509,13 @@
       <color theme="1"/>
       <name val="ＭＳ ゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -1555,29 +1601,51 @@
       <c r="E32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="10"/>
+      <c r="F32" s="10">
+        <v>20</v>
+      </c>
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A33" s="5">
         <v>30</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="10"/>
+      <c r="B33" s="6">
+        <v>45890</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F33" s="10">
+        <v>0</v>
+      </c>
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
       <c r="A34" s="5">
         <v>31</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="10"/>
+      <c r="B34" s="6">
+        <v>45890</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A33474F-8720-40F3-BFBA-51223F3A2B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8D1EEA-09A0-46D7-8DD3-2CD5912FC763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -1652,11 +1652,21 @@
       <c r="A35" s="5">
         <v>32</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
+      <c r="B35" s="6">
+        <v>45890</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="10">
+        <v>20</v>
+      </c>
       <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8D1EEA-09A0-46D7-8DD3-2CD5912FC763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="65">
   <si>
     <t>No.</t>
   </si>
@@ -128,109 +122,256 @@
     <t>54分55秒</t>
   </si>
   <si>
-    <t>solution_2.cs</t>
-  </si>
-  <si>
-    <t>／</t>
-  </si>
-  <si>
-    <t>solution_3.cs</t>
-  </si>
-  <si>
-    <t>B067</t>
-  </si>
-  <si>
-    <t>223分8秒</t>
-  </si>
-  <si>
-    <t>B138</t>
-  </si>
-  <si>
-    <t>51分59秒</t>
-  </si>
-  <si>
-    <t>githubでコメント（PR#1）</t>
-  </si>
-  <si>
-    <t>B045</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 79分14秒</t>
-  </si>
-  <si>
-    <t>githubでコメント（PR#3）</t>
-  </si>
-  <si>
-    <t>solution_4.cs</t>
-  </si>
-  <si>
-    <t>solution_5.cs</t>
-  </si>
-  <si>
-    <t>A078</t>
-  </si>
-  <si>
-    <t>123分57秒</t>
-  </si>
-  <si>
-    <t>B155</t>
-  </si>
-  <si>
-    <t>93分29秒</t>
-  </si>
-  <si>
-    <t>順調に進んでいますね。覚えることが雪だるま式に増えていきますが一歩ずついきましょう～</t>
-  </si>
-  <si>
-    <t>B155</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>solution_2.cs</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>B023</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <r>
-      <t>280</t>
+    <r>
+      <t>paiza</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>の回答結果ページに模範解答が載っていると思います。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>ではなく</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>とかだったと思いますが、そのコードを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chatGPT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>などにコピペして「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>に変換してください」と伝えると、簡単ですが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>版回答が得られますので参考にされてください（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>paiza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>の規約にありますが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>の生成したコードをそのまま</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>paiza</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+      </rPr>
+      <t>に流さないように注意してください）。</t>
+    </r>
+  </si>
+  <si>
+    <t>solution_2.cs</t>
+  </si>
+  <si>
+    <t>／</t>
+  </si>
+  <si>
+    <t>solution_3.cs</t>
+  </si>
+  <si>
+    <t>B067</t>
+  </si>
+  <si>
+    <t>223分8秒</t>
+  </si>
+  <si>
+    <t>B138</t>
+  </si>
+  <si>
+    <t>51分59秒</t>
+  </si>
+  <si>
+    <t>githubでコメント（PR#1）</t>
+  </si>
+  <si>
+    <t>B045</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 79分14秒</t>
+  </si>
+  <si>
+    <t>githubでコメント（PR#3）</t>
+  </si>
+  <si>
+    <t>solution_4.cs</t>
+  </si>
+  <si>
+    <t>solution_5.cs</t>
+  </si>
+  <si>
+    <t>A078</t>
+  </si>
+  <si>
+    <t>123分57秒</t>
+  </si>
+  <si>
+    <t>B155</t>
+  </si>
+  <si>
+    <t>93分29秒</t>
+  </si>
+  <si>
+    <t>順調に進んでいますね。覚えることが雪だるま式に増えていきますが一歩ずついきましょう～</t>
+  </si>
+  <si>
+    <t>B023</t>
+  </si>
+  <si>
+    <r>
+      <t>280</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
-        <charset val="128"/>
       </rPr>
       <t>分</t>
     </r>
-    <rPh sb="3" eb="4">
-      <t>フン</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>solution_3.cs</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>solution_4.cs</t>
-    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>githubでコメント（PR#4）</t>
+  </si>
+  <si>
+    <t>githubでコメント（PR#5）</t>
+  </si>
+  <si>
+    <t>githubでコメント（PR#6）</t>
   </si>
   <si>
     <t>A023</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>solution_1.cs</t>
-    <phoneticPr fontId="5"/>
   </si>
   <si>
     <r>
@@ -239,235 +380,63 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
-        <charset val="128"/>
       </rPr>
       <t>分</t>
     </r>
-    <rPh sb="2" eb="3">
-      <t>フン</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <r>
-      <t>paiza</t>
+  </si>
+  <si>
+    <t>A057</t>
+  </si>
+  <si>
+    <r>
+      <t>87</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
       </rPr>
-      <t>の回答結果ページに模範解答が載っていると思います。</t>
+      <t>分</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>C#</t>
+      <t>14</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ではなく</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
         <family val="2"/>
       </rPr>
-      <t>java</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>とかだったと思いますが、そのコードを</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>chatGPT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>などにコピペして「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>C#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>に変換してください」と伝えると、簡単ですが</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>C#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>版回答が得られますので参考にされてください（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>paiza</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>の規約にありますが、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>の生成したコードをそのまま</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>paiza</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>に流さないように注意してください）。</t>
-    </r>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <r>
-      <t>87</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
       <t>秒</t>
     </r>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>A057</t>
-    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>判定の仕方はよさそうです。数え上げる対象を見直してみましょう（PR#7）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -480,7 +449,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -493,30 +462,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -555,65 +502,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="18">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -624,10 +574,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -665,71 +615,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -757,7 +707,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -780,11 +730,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -793,13 +743,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -809,7 +759,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -818,7 +768,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -827,7 +777,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -835,10 +785,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -903,46 +853,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="49.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="15" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="10.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="17" width="10.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="49.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -965,7 +915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -986,7 +936,7 @@
       </c>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1007,7 +957,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -1028,7 +978,7 @@
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -1049,7 +999,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -1070,7 +1020,7 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -1091,7 +1041,7 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -1112,7 +1062,7 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -1135,7 +1085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -1155,10 +1105,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -1169,17 +1119,17 @@
         <v>32</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="10">
         <v>100</v>
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -1190,17 +1140,17 @@
         <v>32</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="10">
         <v>100</v>
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -1208,20 +1158,20 @@
         <v>45875</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="10">
         <v>0</v>
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -1229,20 +1179,20 @@
         <v>45875</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15" s="10">
         <v>90</v>
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -1250,22 +1200,22 @@
         <v>45875</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="10">
         <v>100</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -1273,22 +1223,22 @@
         <v>45875</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" s="10">
         <v>0</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -1296,22 +1246,22 @@
         <v>45876</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F18" s="10">
         <v>100</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -1322,19 +1272,19 @@
         <v>32</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19" s="10">
         <v>100</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -1345,15 +1295,15 @@
         <v>32</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -1361,22 +1311,22 @@
         <v>45876</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F21" s="10">
         <v>80</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="4" customFormat="1" ht="20.25" customHeight="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -1384,17 +1334,18 @@
         <v>45876</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F22" s="13"/>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7" s="4" customFormat="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -1402,22 +1353,22 @@
         <v>45876</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -1425,20 +1376,20 @@
         <v>45876</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" s="10">
         <v>100</v>
       </c>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -1446,20 +1397,20 @@
         <v>45876</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>56</v>
       </c>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -1467,20 +1418,20 @@
         <v>45887</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>56</v>
       </c>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -1488,20 +1439,22 @@
         <v>45888</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+      <c r="G27" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -1509,20 +1462,22 @@
         <v>45888</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+      <c r="G28" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -1530,20 +1485,22 @@
         <v>45889</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+      <c r="G29" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A30" s="5">
         <v>27</v>
       </c>
@@ -1551,20 +1508,20 @@
         <v>45890</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30" s="10">
         <v>100</v>
       </c>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A31" s="5">
         <v>28</v>
       </c>
@@ -1575,17 +1532,17 @@
         <v>60</v>
       </c>
       <c r="D31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="F31" s="10">
         <v>20</v>
       </c>
       <c r="G31" s="7"/>
     </row>
-    <row r="32" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A32" s="5">
         <v>29</v>
       </c>
@@ -1596,17 +1553,17 @@
         <v>60</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F32" s="10">
         <v>20</v>
       </c>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A33" s="5">
         <v>30</v>
       </c>
@@ -1614,20 +1571,20 @@
         <v>45890</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F33" s="10">
         <v>0</v>
       </c>
       <c r="G33" s="7"/>
     </row>
-    <row r="34" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A34" s="5">
         <v>31</v>
       </c>
@@ -1635,20 +1592,20 @@
         <v>45890</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>56</v>
       </c>
       <c r="G34" s="7"/>
     </row>
-    <row r="35" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A35" s="5">
         <v>32</v>
       </c>
@@ -1659,17 +1616,19 @@
         <v>60</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F35" s="10">
         <v>20</v>
       </c>
-      <c r="G35" s="7"/>
-    </row>
-    <row r="36" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+      <c r="G35" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -1680,7 +1639,7 @@
       <c r="F36" s="10"/>
       <c r="G36" s="7"/>
     </row>
-    <row r="37" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A37" s="5">
         <v>34</v>
       </c>
@@ -1691,7 +1650,7 @@
       <c r="F37" s="10"/>
       <c r="G37" s="7"/>
     </row>
-    <row r="38" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A38" s="5">
         <v>35</v>
       </c>
@@ -1702,7 +1661,7 @@
       <c r="F38" s="10"/>
       <c r="G38" s="7"/>
     </row>
-    <row r="39" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A39" s="5">
         <v>36</v>
       </c>
@@ -1713,7 +1672,7 @@
       <c r="F39" s="10"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A40" s="5">
         <v>37</v>
       </c>
@@ -1724,7 +1683,7 @@
       <c r="F40" s="10"/>
       <c r="G40" s="7"/>
     </row>
-    <row r="41" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A41" s="5">
         <v>38</v>
       </c>
@@ -1735,7 +1694,7 @@
       <c r="F41" s="10"/>
       <c r="G41" s="7"/>
     </row>
-    <row r="42" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A42" s="5">
         <v>39</v>
       </c>
@@ -1746,7 +1705,7 @@
       <c r="F42" s="10"/>
       <c r="G42" s="7"/>
     </row>
-    <row r="43" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A43" s="5">
         <v>40</v>
       </c>
@@ -1757,7 +1716,7 @@
       <c r="F43" s="10"/>
       <c r="G43" s="7"/>
     </row>
-    <row r="44" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A44" s="5">
         <v>41</v>
       </c>
@@ -1768,7 +1727,7 @@
       <c r="F44" s="10"/>
       <c r="G44" s="7"/>
     </row>
-    <row r="45" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A45" s="5">
         <v>42</v>
       </c>
@@ -1779,7 +1738,7 @@
       <c r="F45" s="10"/>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A46" s="5">
         <v>43</v>
       </c>
@@ -1790,7 +1749,7 @@
       <c r="F46" s="10"/>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A47" s="5">
         <v>44</v>
       </c>
@@ -1801,7 +1760,7 @@
       <c r="F47" s="10"/>
       <c r="G47" s="7"/>
     </row>
-    <row r="48" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A48" s="5">
         <v>45</v>
       </c>
@@ -1812,7 +1771,7 @@
       <c r="F48" s="10"/>
       <c r="G48" s="7"/>
     </row>
-    <row r="49" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A49" s="5">
         <v>46</v>
       </c>
@@ -1823,7 +1782,7 @@
       <c r="F49" s="10"/>
       <c r="G49" s="7"/>
     </row>
-    <row r="50" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A50" s="5">
         <v>47</v>
       </c>
@@ -1834,7 +1793,7 @@
       <c r="F50" s="10"/>
       <c r="G50" s="7"/>
     </row>
-    <row r="51" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A51" s="5">
         <v>48</v>
       </c>
@@ -1845,7 +1804,7 @@
       <c r="F51" s="10"/>
       <c r="G51" s="7"/>
     </row>
-    <row r="52" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A52" s="5">
         <v>49</v>
       </c>
@@ -1856,7 +1815,7 @@
       <c r="F52" s="10"/>
       <c r="G52" s="7"/>
     </row>
-    <row r="53" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A53" s="5">
         <v>50</v>
       </c>
@@ -1867,7 +1826,7 @@
       <c r="F53" s="10"/>
       <c r="G53" s="7"/>
     </row>
-    <row r="54" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A54" s="5">
         <v>51</v>
       </c>
@@ -1878,7 +1837,7 @@
       <c r="F54" s="10"/>
       <c r="G54" s="7"/>
     </row>
-    <row r="55" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A55" s="5">
         <v>52</v>
       </c>
@@ -1889,7 +1848,7 @@
       <c r="F55" s="10"/>
       <c r="G55" s="7"/>
     </row>
-    <row r="56" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A56" s="5">
         <v>53</v>
       </c>
@@ -1900,7 +1859,7 @@
       <c r="F56" s="10"/>
       <c r="G56" s="7"/>
     </row>
-    <row r="57" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A57" s="5">
         <v>54</v>
       </c>
@@ -1911,7 +1870,7 @@
       <c r="F57" s="10"/>
       <c r="G57" s="7"/>
     </row>
-    <row r="58" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A58" s="5">
         <v>55</v>
       </c>
@@ -1922,7 +1881,7 @@
       <c r="F58" s="10"/>
       <c r="G58" s="7"/>
     </row>
-    <row r="59" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A59" s="5">
         <v>56</v>
       </c>
@@ -1933,7 +1892,7 @@
       <c r="F59" s="10"/>
       <c r="G59" s="7"/>
     </row>
-    <row r="60" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A60" s="5">
         <v>57</v>
       </c>
@@ -1944,7 +1903,7 @@
       <c r="F60" s="10"/>
       <c r="G60" s="7"/>
     </row>
-    <row r="61" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A61" s="5">
         <v>58</v>
       </c>
@@ -1955,7 +1914,7 @@
       <c r="F61" s="10"/>
       <c r="G61" s="7"/>
     </row>
-    <row r="62" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A62" s="5">
         <v>59</v>
       </c>
@@ -1966,7 +1925,7 @@
       <c r="F62" s="10"/>
       <c r="G62" s="7"/>
     </row>
-    <row r="63" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A63" s="5">
         <v>60</v>
       </c>
@@ -1977,7 +1936,7 @@
       <c r="F63" s="10"/>
       <c r="G63" s="7"/>
     </row>
-    <row r="64" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A64" s="5">
         <v>61</v>
       </c>
@@ -1988,7 +1947,7 @@
       <c r="F64" s="10"/>
       <c r="G64" s="7"/>
     </row>
-    <row r="65" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A65" s="5">
         <v>62</v>
       </c>
@@ -1999,7 +1958,7 @@
       <c r="F65" s="10"/>
       <c r="G65" s="7"/>
     </row>
-    <row r="66" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A66" s="5">
         <v>63</v>
       </c>
@@ -2010,7 +1969,7 @@
       <c r="F66" s="10"/>
       <c r="G66" s="7"/>
     </row>
-    <row r="67" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A67" s="5">
         <v>64</v>
       </c>
@@ -2021,7 +1980,7 @@
       <c r="F67" s="10"/>
       <c r="G67" s="7"/>
     </row>
-    <row r="68" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A68" s="5">
         <v>65</v>
       </c>
@@ -2032,7 +1991,7 @@
       <c r="F68" s="10"/>
       <c r="G68" s="7"/>
     </row>
-    <row r="69" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A69" s="5">
         <v>66</v>
       </c>
@@ -2043,7 +2002,7 @@
       <c r="F69" s="10"/>
       <c r="G69" s="7"/>
     </row>
-    <row r="70" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A70" s="5">
         <v>67</v>
       </c>
@@ -2054,7 +2013,7 @@
       <c r="F70" s="10"/>
       <c r="G70" s="7"/>
     </row>
-    <row r="71" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A71" s="5">
         <v>68</v>
       </c>
@@ -2065,7 +2024,7 @@
       <c r="F71" s="10"/>
       <c r="G71" s="7"/>
     </row>
-    <row r="72" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A72" s="5">
         <v>69</v>
       </c>
@@ -2076,7 +2035,7 @@
       <c r="F72" s="10"/>
       <c r="G72" s="7"/>
     </row>
-    <row r="73" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A73" s="5">
         <v>70</v>
       </c>
@@ -2087,7 +2046,7 @@
       <c r="F73" s="10"/>
       <c r="G73" s="7"/>
     </row>
-    <row r="74" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A74" s="5">
         <v>71</v>
       </c>
@@ -2098,7 +2057,7 @@
       <c r="F74" s="10"/>
       <c r="G74" s="7"/>
     </row>
-    <row r="75" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A75" s="5">
         <v>72</v>
       </c>
@@ -2109,7 +2068,7 @@
       <c r="F75" s="10"/>
       <c r="G75" s="7"/>
     </row>
-    <row r="76" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A76" s="5">
         <v>73</v>
       </c>
@@ -2120,7 +2079,7 @@
       <c r="F76" s="10"/>
       <c r="G76" s="7"/>
     </row>
-    <row r="77" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A77" s="5">
         <v>74</v>
       </c>
@@ -2131,7 +2090,7 @@
       <c r="F77" s="10"/>
       <c r="G77" s="7"/>
     </row>
-    <row r="78" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A78" s="5">
         <v>75</v>
       </c>
@@ -2142,7 +2101,7 @@
       <c r="F78" s="10"/>
       <c r="G78" s="7"/>
     </row>
-    <row r="79" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A79" s="5">
         <v>76</v>
       </c>
@@ -2153,7 +2112,7 @@
       <c r="F79" s="10"/>
       <c r="G79" s="7"/>
     </row>
-    <row r="80" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A80" s="5">
         <v>77</v>
       </c>
@@ -2164,7 +2123,7 @@
       <c r="F80" s="10"/>
       <c r="G80" s="7"/>
     </row>
-    <row r="81" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A81" s="5">
         <v>78</v>
       </c>
@@ -2175,7 +2134,7 @@
       <c r="F81" s="10"/>
       <c r="G81" s="7"/>
     </row>
-    <row r="82" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A82" s="5">
         <v>79</v>
       </c>
@@ -2186,7 +2145,7 @@
       <c r="F82" s="10"/>
       <c r="G82" s="7"/>
     </row>
-    <row r="83" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A83" s="5">
         <v>80</v>
       </c>
@@ -2197,7 +2156,7 @@
       <c r="F83" s="10"/>
       <c r="G83" s="7"/>
     </row>
-    <row r="84" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A84" s="5">
         <v>81</v>
       </c>
@@ -2208,7 +2167,7 @@
       <c r="F84" s="10"/>
       <c r="G84" s="7"/>
     </row>
-    <row r="85" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A85" s="5">
         <v>82</v>
       </c>
@@ -2219,7 +2178,7 @@
       <c r="F85" s="10"/>
       <c r="G85" s="7"/>
     </row>
-    <row r="86" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A86" s="5">
         <v>83</v>
       </c>
@@ -2230,7 +2189,7 @@
       <c r="F86" s="10"/>
       <c r="G86" s="7"/>
     </row>
-    <row r="87" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A87" s="5">
         <v>84</v>
       </c>
@@ -2241,7 +2200,7 @@
       <c r="F87" s="10"/>
       <c r="G87" s="7"/>
     </row>
-    <row r="88" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A88" s="5">
         <v>85</v>
       </c>
@@ -2252,7 +2211,7 @@
       <c r="F88" s="10"/>
       <c r="G88" s="7"/>
     </row>
-    <row r="89" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A89" s="5">
         <v>86</v>
       </c>
@@ -2263,7 +2222,7 @@
       <c r="F89" s="10"/>
       <c r="G89" s="7"/>
     </row>
-    <row r="90" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A90" s="5">
         <v>87</v>
       </c>
@@ -2274,7 +2233,7 @@
       <c r="F90" s="10"/>
       <c r="G90" s="7"/>
     </row>
-    <row r="91" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A91" s="5">
         <v>88</v>
       </c>
@@ -2285,7 +2244,7 @@
       <c r="F91" s="10"/>
       <c r="G91" s="7"/>
     </row>
-    <row r="92" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A92" s="5">
         <v>89</v>
       </c>
@@ -2296,7 +2255,7 @@
       <c r="F92" s="10"/>
       <c r="G92" s="7"/>
     </row>
-    <row r="93" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A93" s="5">
         <v>90</v>
       </c>
@@ -2307,7 +2266,7 @@
       <c r="F93" s="10"/>
       <c r="G93" s="7"/>
     </row>
-    <row r="94" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A94" s="5">
         <v>91</v>
       </c>
@@ -2318,7 +2277,7 @@
       <c r="F94" s="10"/>
       <c r="G94" s="7"/>
     </row>
-    <row r="95" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A95" s="5">
         <v>92</v>
       </c>
@@ -2329,7 +2288,7 @@
       <c r="F95" s="10"/>
       <c r="G95" s="7"/>
     </row>
-    <row r="96" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A96" s="5">
         <v>93</v>
       </c>
@@ -2340,7 +2299,7 @@
       <c r="F96" s="10"/>
       <c r="G96" s="7"/>
     </row>
-    <row r="97" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A97" s="5">
         <v>94</v>
       </c>
@@ -2351,7 +2310,7 @@
       <c r="F97" s="10"/>
       <c r="G97" s="7"/>
     </row>
-    <row r="98" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A98" s="5">
         <v>95</v>
       </c>
@@ -2362,7 +2321,7 @@
       <c r="F98" s="10"/>
       <c r="G98" s="7"/>
     </row>
-    <row r="99" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A99" s="5">
         <v>96</v>
       </c>
@@ -2373,7 +2332,7 @@
       <c r="F99" s="10"/>
       <c r="G99" s="7"/>
     </row>
-    <row r="100" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A100" s="5">
         <v>97</v>
       </c>
@@ -2384,7 +2343,7 @@
       <c r="F100" s="10"/>
       <c r="G100" s="7"/>
     </row>
-    <row r="101" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A101" s="5">
         <v>98</v>
       </c>
@@ -2395,7 +2354,7 @@
       <c r="F101" s="10"/>
       <c r="G101" s="7"/>
     </row>
-    <row r="102" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A102" s="5">
         <v>99</v>
       </c>
@@ -2406,7 +2365,7 @@
       <c r="F102" s="10"/>
       <c r="G102" s="7"/>
     </row>
-    <row r="103" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A103" s="5">
         <v>100</v>
       </c>
@@ -2418,8 +2377,6 @@
       <c r="G103" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8D1EEA-09A0-46D7-8DD3-2CD5912FC763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1457A973-6EA6-441B-AD49-9F8EF43962F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -1673,11 +1673,21 @@
       <c r="A36" s="5">
         <v>33</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="10"/>
+      <c r="B36" s="6">
+        <v>45891</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="10">
+        <v>100</v>
+      </c>
       <c r="G36" s="7"/>
     </row>
     <row r="37" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1457A973-6EA6-441B-AD49-9F8EF43962F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184BA144-B31F-49EF-B832-68144C469A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -1694,11 +1694,21 @@
       <c r="A37" s="5">
         <v>34</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="10"/>
+      <c r="B37" s="6">
+        <v>45891</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="10">
+        <v>100</v>
+      </c>
       <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184BA144-B31F-49EF-B832-68144C469A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208CD3CD-BF47-487E-9D7C-C2700D4BA179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -456,6 +456,45 @@
   </si>
   <si>
     <t>A057</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>A032</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <t>263</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>秒</t>
+    </r>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1616,9 +1655,6 @@
       <c r="C33" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="E33" s="7" t="s">
         <v>64</v>
       </c>
@@ -1715,11 +1751,21 @@
       <c r="A38" s="5">
         <v>35</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="10"/>
+      <c r="B38" s="6">
+        <v>45891</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38" s="10">
+        <v>0</v>
+      </c>
       <c r="G38" s="7"/>
     </row>
     <row r="39" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208CD3CD-BF47-487E-9D7C-C2700D4BA179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CFEDFA-F262-4DE6-AF06-C71BF4FC7117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -1772,11 +1772,21 @@
       <c r="A39" s="5">
         <v>36</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="10"/>
+      <c r="B39" s="6">
+        <v>45894</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" s="10">
+        <v>70</v>
+      </c>
       <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CFEDFA-F262-4DE6-AF06-C71BF4FC7117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A3F7E2-B183-4E71-A40F-276E4C7A9A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -1793,11 +1793,21 @@
       <c r="A40" s="5">
         <v>37</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="10"/>
+      <c r="B40" s="6">
+        <v>45894</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="10">
+        <v>80</v>
+      </c>
       <c r="G40" s="7"/>
     </row>
     <row r="41" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">

--- a/paiza-training/02_スキルチェック一覧.xlsx
+++ b/paiza-training/02_スキルチェック一覧.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\CSV2404-0002\backup\m-matsumoto\入社教育\2. C#基礎\Paiza-Training\paiza-training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A3F7E2-B183-4E71-A40F-276E4C7A9A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6541EACF-D1DF-401C-8ECC-F92EB342B798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -1814,11 +1814,21 @@
       <c r="A41" s="5">
         <v>38</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="10"/>
+      <c r="B41" s="6">
+        <v>45894</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1">
